--- a/group_comparison/five_cohort_sample_comparison_dashboard_default_colors.xlsx
+++ b/group_comparison/five_cohort_sample_comparison_dashboard_default_colors.xlsx
@@ -23,8 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean length plot" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Median identity plot" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean identity plot" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Median mapping Q score plot" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean mapping Q score plot" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Median identity Q score plot" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean identity Q score plot" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yield (Gb) vs. med. idy" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N50 (kb) vs. med. idy" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pct. total vs. med. idy" sheetId="22" state="visible" r:id="rId22"/>
@@ -1632,7 +1632,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Median mapping Q score</t>
+          <t>Median identity Q score</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1660,7 +1660,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mean mapping Q score</t>
+          <t>Mean identity Q score</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2220,7 +2220,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Median mapping Q score</t>
+          <t>Median identity Q score</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2248,7 +2248,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mean mapping Q score</t>
+          <t>Mean identity Q score</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2808,7 +2808,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Median mapping Q score</t>
+          <t>Median identity Q score</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2836,7 +2836,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mean mapping Q score</t>
+          <t>Mean identity Q score</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3284,7 +3284,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Median mapping Q score</t>
+          <t>Median identity Q score</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3312,7 +3312,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mean mapping Q score</t>
+          <t>Mean identity Q score</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3732,7 +3732,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Median mapping Q score</t>
+          <t>Median identity Q score</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3760,7 +3760,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mean mapping Q score</t>
+          <t>Mean identity Q score</t>
         </is>
       </c>
       <c r="B15" t="n">
